--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45037</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44531</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44140</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>44467</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44445</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>44159</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45337</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44237</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45050</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45809</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44139</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44139</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44208</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44083</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44055</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44068.82011574074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44113</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44166</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44124</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44179</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44356</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44273</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>44279</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44140</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44572</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44551</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44342</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44284</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44152</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44285</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44585</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>44120</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44585</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44468</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44687</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44670</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44458</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44139</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44501</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44421</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44368</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44449</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44406</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44441</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44384</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44705</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44435</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44103</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44222</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44167</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44365</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44399</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44241</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44503</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44140</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44498</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44497</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44806</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44343</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44154</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44256</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44424</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44624</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44874</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44742</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44442</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44208</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44629</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44364</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44267</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44354</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44441</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44501.61</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44572</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44420</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44300</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44491</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44270</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44267</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44452</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44088</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44476</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44123</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44088</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44623</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44188</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44133</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44621</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44365</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44333</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44440</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44209</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44322</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44742</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44305</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44747</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44075</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44113</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44687</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44204</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44062</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44053</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44208</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44125</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44057</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44217</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44146</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44286</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44425</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44440</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>44300</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44140</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44847</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44306</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44466</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44225</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44711</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44132</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44131</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44706</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44053</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44342</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44060</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44596</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44207</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44657</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44858</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>44608</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44579</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44284</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44302</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44132</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44698</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>45238</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45085</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45683</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45744</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44890</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45340</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45080</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45713</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45159</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45048</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45247</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44309</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45512</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44825</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45077</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44090</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45042</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45166</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45362</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45532</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44881</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45204</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45264</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44302</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44305</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44461</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44860</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45092</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45234</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45733.43296296296</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45538</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45538</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45091</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45254</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>44860</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45174</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44903</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45662</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44967</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44847</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45251</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45772</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45126</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44930</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44866</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45094</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45212</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45093</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45707</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45443</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>44461</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45103</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45315</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45034</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>44053</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45127</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45443</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45085</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45085</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45082</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45108</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45483</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45733</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45733</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45050</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44054</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45118</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45721.66482638889</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45749</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44055</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45245.655</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45631</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45587</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45483</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45733</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45733</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45551</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45600</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45766</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>44473</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45107</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45342</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>44628</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45107</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44939</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45475</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45538</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45030</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45621</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45075</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45625</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45344.695</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45499</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>45594</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>44144</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45499</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44893.475</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45782</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>44433</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45524.35423611111</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45524</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>44398</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45133</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44879</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44592</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45020</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45551</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44584</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>44988</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45050</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>44614</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>44981</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45554</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45084</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45785</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45415</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44512</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45742</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45048</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45475</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45453</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45789.45167824074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45789.50225694444</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44911</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44200</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45181</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45163</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45789.50484953704</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45789.46831018518</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>44496</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45335</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44204</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45657</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>44302</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45643.84206018518</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>44693</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>44920</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44596</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45719</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45324</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44186</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44305</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45711</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>45631</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>44559</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45558</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>44553</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>44523</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45328</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45057</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44624</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45142</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45162</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44169</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45358</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>45838</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45085</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45839</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44799</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44636</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45092</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44586</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45722</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45012</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45170</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45015</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45643</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44754</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44619</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>44837</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45770</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>44967</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45316</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>44700</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45841</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45256.91383101852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45092</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45057</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44725</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44706</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>45012</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45707</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45693</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45079</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45761</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45266</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45133</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45334</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45827</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>44616</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45846</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45846</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45117</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45846</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>44936</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45055</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45697</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>44742</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45004</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>45142</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45631</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>44757</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45178</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45685</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44323</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>44747</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>44349</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45238</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>44820</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45755</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45180</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>45783</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>45256</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42267,7 +42267,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>44080</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45754</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45148</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44862</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44988</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>44062.55398148148</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>44516</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45027</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>44753</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45303</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45113</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>44930</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45561</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>44748</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44435</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45019</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>44874</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45166</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45832</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>44636</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45140</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45070</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>44281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45301</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45335</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>44350</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45602</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45089</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>44893</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>44517</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45610</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>44543</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>44235</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45183</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>44235</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>44323</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>44284</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>45579</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44120</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45162</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>44741</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>45635</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>45217</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44580</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48480,7 +48480,7 @@
         <v>44139</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>44909</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48651,7 +48651,7 @@
         <v>45035</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48936,7 +48936,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45568</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45568</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49221,7 +49221,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>44441</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45104</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>44942</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>44875</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45573</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45581.49081018518</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>45106</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>44998</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50418,7 +50418,7 @@
         <v>45324</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45012</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45037</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44531</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44140</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>44467</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44445</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>44159</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45337</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44237</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45050</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45809</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44139</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44139</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44208</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44083</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44055</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44068.82011574074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44113</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44166</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44124</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44179</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44356</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44273</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>44279</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44140</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44572</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44551</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44342</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44284</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44152</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44285</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44585</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>44120</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44585</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44468</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44687</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44670</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44458</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44139</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44501</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44421</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44368</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44449</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44406</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44441</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44384</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44705</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44435</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44103</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44222</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44167</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44365</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44399</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44241</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44503</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44140</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44498</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44497</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44806</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44343</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44154</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44256</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44424</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44624</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44874</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44742</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44442</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44208</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44629</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44364</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44267</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44354</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44441</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44501.61</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44572</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44420</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44300</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44491</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44270</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44267</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44452</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44088</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44476</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44123</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44088</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44623</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44188</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44133</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44621</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44365</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44333</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44440</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44209</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44322</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44742</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44305</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44747</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44075</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44113</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44687</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44204</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44062</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44053</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44208</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44125</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44057</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44217</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44146</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44286</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44425</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44440</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>44300</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44140</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44847</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44306</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44466</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44225</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44711</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44132</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44131</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44706</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44053</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44342</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44060</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44596</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44207</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44657</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44858</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>44608</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44579</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44284</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44302</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44132</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44698</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>45238</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45085</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45683</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45744</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44890</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45340</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45080</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45713</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45159</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45048</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45247</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44309</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45512</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44825</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45077</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44090</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45042</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45166</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45362</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45532</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44881</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45204</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45264</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44302</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44305</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44461</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44860</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45092</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45234</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45733.43296296296</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45538</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45538</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45091</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45254</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>44860</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45174</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44903</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45662</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44967</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44847</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45251</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45772</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45126</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44930</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44866</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45094</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45212</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45093</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45707</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45443</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>44461</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45103</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45315</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45034</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>44053</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45127</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45443</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45085</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45085</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45082</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45108</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45483</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45733</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45733</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45050</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44054</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45118</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45721.66482638889</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45749</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44055</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45245.655</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45631</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45587</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45483</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45733</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45733</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45551</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45600</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45766</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>44473</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45107</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45342</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>44628</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45107</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44939</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45475</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45538</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45030</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45621</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45075</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45625</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45344.695</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45499</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>45594</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>44144</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45499</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44893.475</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45782</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>44433</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45524.35423611111</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45524</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>44398</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45133</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44879</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44592</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45020</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45551</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44584</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>44988</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45050</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>44614</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>44981</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45554</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45084</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45785</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45415</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44512</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45742</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45048</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45475</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45453</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45789.45167824074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45789.50225694444</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44911</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44200</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45181</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45163</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45789.50484953704</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45789.46831018518</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>44496</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45335</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44204</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45657</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>44302</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45643.84206018518</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>44693</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>44920</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44596</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45719</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45324</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44186</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44305</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45711</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>45631</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>44559</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45558</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>44553</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>44523</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45328</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45057</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44624</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45142</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45162</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44169</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45358</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>45838</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45085</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45839</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44799</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44636</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45092</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44586</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45722</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45012</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45170</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45015</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45643</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44754</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44619</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>44837</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45770</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>44967</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45316</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>44700</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45841</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45256.91383101852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45092</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45057</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44725</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44706</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>45012</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45707</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45693</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45079</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45761</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45266</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45133</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45334</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45827</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>44616</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45846</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45846</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45117</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45846</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>44936</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45055</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45697</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>44742</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45004</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>45142</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45631</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>44757</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45178</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45685</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44323</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>44747</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>44349</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45238</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>44820</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45755</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45180</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>45783</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>45256</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42267,7 +42267,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>44080</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45754</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45148</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44862</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44988</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>44062.55398148148</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>44516</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45027</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>44753</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45303</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45113</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>44930</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45561</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>44748</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44435</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45019</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>44874</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45166</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45832</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>44636</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45140</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45070</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>44281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45301</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45335</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>44350</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45602</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45089</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>44893</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>44517</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45610</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>44543</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>44235</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45183</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>44235</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>44323</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>44284</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>45579</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44120</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45162</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>44741</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>45635</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>45217</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44580</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48480,7 +48480,7 @@
         <v>44139</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>44909</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48651,7 +48651,7 @@
         <v>45035</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48936,7 +48936,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45568</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45568</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49221,7 +49221,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>44441</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45104</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>44942</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>44875</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45573</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45581.49081018518</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>45106</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>44998</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50418,7 +50418,7 @@
         <v>45324</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45012</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44531</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44140</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>44467</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44445</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45809</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45050</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44237</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44139</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44139</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44159</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45337</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44208</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44083</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44068.82011574074</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44113</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44124</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44179</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44356</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44273</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44279</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44140</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44572</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44551</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44342</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44152</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44285</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44284</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44585</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44600</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44120</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>44468</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44585</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44687</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44670</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44458</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44139</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44501</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44421</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44368</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44449</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44406</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44441</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44384</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44375</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44705</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44435</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44222</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44103</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44167</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44365</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44399</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44241</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44498</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44140</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44806</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44343</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44154</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44424</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44624</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44874</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44442</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44742</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44208</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44629</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44364</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44267</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44354</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44350</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44441</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44501.61</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44572</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44420</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44599</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44491</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44300</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44270</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44452</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44476</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44123</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44088</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44623</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44188</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44440</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44742</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44322</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44305</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>44747</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44075</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44113</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44687</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>44204</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>44062</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>44208</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44125</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44217</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44146</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44286</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44425</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44440</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>44300</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>44847</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44466</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44306</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44140</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44225</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44259</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44711</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44132</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44131</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44342</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44596</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44207</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44284</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44302</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44608</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44579</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44132</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44657</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44858</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44133</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44698</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44365</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44621</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45683</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44209</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44881</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44333</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45204</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45713</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45245.655</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45733</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45733</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45092</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45247</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>44309</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45512</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44825</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45600</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45766</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45551</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45042</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45342</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45538</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44903</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45362</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45107</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45621</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45075</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45625</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45344.695</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45499</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44628</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45594</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45107</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45782</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44967</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44398</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45133</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44879</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45020</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44981</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45785</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45084</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45475</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45415</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45453</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>44512</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45789.45167824074</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45789.50225694444</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45048</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45789.46831018518</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44496</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45163</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45335</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44559</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45643.84206018518</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45126</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45358</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>44596</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45719</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45631</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45558</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44837</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45770</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45841</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44553</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44523</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44624</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45012</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45162</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>44169</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>44799</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44636</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45334</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45092</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>44586</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>45827</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44866</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45170</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45643</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44461</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44754</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45714</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45315</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45127</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45443</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>45057</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>44725</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>44706</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45707</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45693</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45761</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45483</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45133</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>44616</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44473</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45697</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44939</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45475</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45030</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>44144</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45499</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>44893.475</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45783</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>44433</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45524.35423611111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45524</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>44592</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45551</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44584</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>44757</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44988</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45050</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45554</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45238</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45755</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45180</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45742</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45561</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>44911</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45832</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>44200</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44862</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44062.55398148148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44753</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44204</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45303</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45019</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45657</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45256</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44874</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45166</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44636</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>45140</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45070</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44281</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45301</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>44693</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45880</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45880</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45335</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44920</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45838</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45880</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44350</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45711</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45324</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>44186</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45602</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45089</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45846</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>44893</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44517</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45610</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45057</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45142</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45846</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44543</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45085</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>44235</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45722</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45012</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>45183</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45015</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>44619</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>44235</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>44323</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>44967</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45316</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44700</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45092</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44284</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45579</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45079</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>44120</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45266</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45162</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>44741</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45635</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45217</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>44580</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45117</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>44139</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>44936</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45055</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>44909</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45004</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45035</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>45142</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45568</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45568</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45631</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45178</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45069</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44441</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45685</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44323</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>45104</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>44942</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>44747</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44349</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>44875</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45573</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45581.49081018518</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>45106</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44080</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45754</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>44988</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>44516</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>44998</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45324</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45012</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45027</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45085</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>44930</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45340</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45159</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>44748</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>44435</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45238</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45744</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45085</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>44890</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45080</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>44305</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45077</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>44090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45166</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45532</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45254</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45174</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45662</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44302</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44461</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>44860</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45234</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45733.43296296296</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45538</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45538</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45251</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45091</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45094</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45212</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45707</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45443</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45328</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45092</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44847</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45034</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45772</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45085</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45082</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45483</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44930</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48998,7 +48998,7 @@
         <v>45118</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45093</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45749</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49568,7 +49568,7 @@
         <v>45631</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45587</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>45103</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45108</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45733</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45733</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45050</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44531</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44140</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>44467</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44445</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45809</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45050</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44237</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44139</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44139</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44159</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45337</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44208</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44083</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44068.82011574074</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44113</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44124</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44179</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44356</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44273</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44279</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44140</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44572</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44551</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44342</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44152</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44285</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44284</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44585</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44600</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44120</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>44468</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44585</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44687</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44670</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44458</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44139</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44501</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44421</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44368</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44449</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44406</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44441</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44384</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44375</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44705</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44435</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44222</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44103</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44167</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44365</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44399</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44241</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44498</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44140</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44806</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44343</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44154</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44424</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44624</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44874</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44442</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44742</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44208</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44629</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44364</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44267</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44354</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44350</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44441</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44501.61</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44572</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44420</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44599</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44491</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44300</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44270</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44452</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44476</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44123</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44088</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44623</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44188</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44440</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44742</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44322</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44305</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>44747</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44075</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44113</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44687</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>44204</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>44062</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>44208</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44125</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44217</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44146</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44286</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44425</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44440</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>44300</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>44847</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44466</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44306</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44140</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44225</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44259</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44711</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44132</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44131</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44342</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44596</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44207</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44284</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44302</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44608</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44579</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44132</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44657</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44858</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44133</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44698</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44365</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44621</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45683</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44209</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44881</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44333</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45204</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45713</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45245.655</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45733</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45733</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45092</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45247</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>44309</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45512</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44825</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45600</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45766</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45551</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45042</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45342</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45538</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44903</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45362</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45107</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45621</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45075</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45625</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45344.695</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45499</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44628</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45594</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45107</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45782</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44967</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44398</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45133</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44879</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45020</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44981</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45785</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45084</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45475</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45415</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45453</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>44512</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45789.45167824074</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45789.50225694444</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45048</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45789.46831018518</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44496</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45163</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45335</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44559</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45643.84206018518</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45126</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45358</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>44596</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45719</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45631</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45558</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44837</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45770</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45841</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44553</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44523</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44624</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45012</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45162</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>44169</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>44799</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44636</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45334</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45092</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>44586</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>45827</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44866</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45170</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45643</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44461</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44754</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45714</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45315</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45127</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45443</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>45057</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>44725</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>44706</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45707</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45693</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45761</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45483</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45133</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>44616</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44473</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45697</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44939</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45475</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45030</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>44144</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45499</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>44893.475</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45783</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>44433</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45524.35423611111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45524</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>44592</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45551</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44584</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>44757</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44988</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45050</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45554</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45238</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45755</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45180</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45742</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45561</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>44911</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45832</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>44200</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44862</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44062.55398148148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44753</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44204</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45303</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45019</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45657</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45256</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44874</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45166</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44636</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>45140</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45070</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44281</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45301</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>44693</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45880</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45880</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45335</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44920</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45838</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45880</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44350</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45711</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45324</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>44186</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45602</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45089</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45846</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>44893</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44517</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45610</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45057</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45142</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45846</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44543</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45085</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>44235</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45722</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45012</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>45183</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45015</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>44619</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>44235</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>44323</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>44967</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45316</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44700</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45092</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44284</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45579</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45079</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>44120</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45266</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45162</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>44741</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45635</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45217</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>44580</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45117</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>44139</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>44936</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45055</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>44909</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45004</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45035</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>45142</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45568</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45568</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45631</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45178</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45069</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44441</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45685</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44323</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>45104</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>44942</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>44747</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44349</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>44875</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45573</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45581.49081018518</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>45106</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44080</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45754</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>44988</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>44516</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>44998</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45324</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45012</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45027</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45085</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>44930</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45340</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45159</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>44748</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>44435</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45238</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45744</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45085</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>44890</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45080</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>44305</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45077</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>44090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45166</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45532</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45254</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45174</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45662</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44302</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44461</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>44860</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45234</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45733.43296296296</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45538</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45538</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45251</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45091</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45094</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45212</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45707</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45443</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45328</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45092</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44847</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45034</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45772</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45085</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45082</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45483</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44930</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48998,7 +48998,7 @@
         <v>45118</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45093</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45749</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49568,7 +49568,7 @@
         <v>45631</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45587</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>45103</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45108</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45733</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45733</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45050</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45037</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44531</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44140</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>44467</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45337</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>44237</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44139</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45050</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44139</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44445</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44159</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45809</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44208</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44083</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44068.82011574074</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44113</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44124</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44179</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44356</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44273</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44279</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44572</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44140</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44551</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44342</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44284</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44285</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44152</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44585</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44600</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44120</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>44585</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44670</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44687</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44458</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44139</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44501</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44421</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44406</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44449</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44384</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44502</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44375</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44435</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44705</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44167</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44365</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44399</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44241</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44368</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44103</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44498</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44140</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44806</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44343</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44154</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44424</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44624</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44442</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44874</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44742</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44629</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44208</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44267</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44364</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44354</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44350</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44441</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44501.61</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44572</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44420</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44599</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44300</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44491</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44270</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44452</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44476</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44123</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44088</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44623</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44188</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44621</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44133</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44333</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44440</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44209</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44322</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44305</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44747</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44113</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44075</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44687</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44204</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44217</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44125</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44146</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44286</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44208</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44300</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44425</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44306</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44440</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44225</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>44466</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44140</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44711</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44132</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44706</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44342</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44596</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44131</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44207</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44608</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44657</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44579</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45035</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45106</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45761</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44284</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>44517</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44302</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45027</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44132</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44698</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45079</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45573</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44235</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45217</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45713</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>44967</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45212</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44700</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45631</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45744</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45183</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44120</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44998</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45579</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45108</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45643</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44747</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45107</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45340</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44860</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44911</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44890</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44616</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44875</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45538</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45012</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45092</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44909</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45019</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45635</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44433</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45118</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44302</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>44936</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45166</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44753</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45362</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45034</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>44862</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45685</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45587</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44553</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45117</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45266</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45142</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>44847</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44930</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45693</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44305</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45057</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>44693</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44323</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>44967</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45020</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45113</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45162</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>44879</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45077</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45301</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44281</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45030</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44942</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>44323</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44981</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45554</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>44596</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45048</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45719</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45015</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45075</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45625</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45610</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45538</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45594</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45344.695</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45499</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45328</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44706</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>45621</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45551</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44398</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45782</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45483</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45335</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>44757</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>45324</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45127</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45785</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45512</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44543</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45707</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45328</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45107</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45103</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44350</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45754</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45749</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>44496</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>44930</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45453</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45475</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45234</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45755</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45082</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>44636</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45085</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45568</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44988</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44584</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>44592</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45358</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44614</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44559</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45551</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45303</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45085</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>44799</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44302</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45538</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>44349</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45443</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>44169</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45766</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45057</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45475</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>44754</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45092</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45483</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>45770</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44903</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45069</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45238</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44837</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45841</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44580</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45012</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45334</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45600</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45245.655</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45050</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45204</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>44284</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45827</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45532</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>44881</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45581.49081018518</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45254</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>44920</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45733</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>45733</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45697</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45048</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>45733</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45733</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44825</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45085</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45085</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45055</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>44586</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45683</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>44820</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>44200</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>44725</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44988</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45722</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>44441</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>44516</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45080</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>45783</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>44186</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45247</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>44435</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45174</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45443</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45499</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44523</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45524</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>44866</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>44305</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>44204</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45264</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45126</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45558</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45093</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>44080</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>44235</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45561</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>45238</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>45662</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45631</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>44636</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45342</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44309</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45707</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>44624</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>44939</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45832</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>45178</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>44860</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>44893</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44820</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45142</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45050</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45251</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>45316</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44139</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45094</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45714</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45084</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44461</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>45335</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45839</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45838</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45880</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45846</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45880</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45711</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45140</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45256</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>44619</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45180</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45772</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45133</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45846</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45181</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45631</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45887.44987268518</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45133</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45887.44877314815</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>44874</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>45887.44629629629</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45887.49454861111</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45846</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45324</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45170</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45042</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45162</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>44144</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>44893.475</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45602</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45415</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45733.43296296296</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45891.58806712963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45091</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45890</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45085</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45012</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45159</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44461</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48998,7 +48998,7 @@
         <v>45092</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45657</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>44742</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49568,7 +49568,7 @@
         <v>44628</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45148</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45037</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44531</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44140</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>44467</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45337</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>44237</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44139</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45050</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44139</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44445</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44159</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45809</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44208</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44083</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44068.82011574074</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44113</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44124</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44179</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44356</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44273</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44279</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44572</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44140</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44551</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44342</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44284</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44285</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44152</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44585</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44600</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44120</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>44585</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44670</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44687</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44458</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44139</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44501</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44421</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44406</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44449</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44384</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44502</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44375</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44435</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44705</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44167</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44365</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44399</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44241</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44368</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44103</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44498</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44140</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44806</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44343</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44154</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44424</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44624</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44442</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44874</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44742</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44629</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44208</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44267</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44364</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44354</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44350</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44441</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44501.61</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44572</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44420</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44599</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44300</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44491</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44270</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44452</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44476</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44123</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44088</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44623</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44188</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44621</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44133</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44333</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44440</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44209</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44322</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44305</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44747</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44113</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44075</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44687</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44204</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44217</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44125</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44146</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44286</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44208</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44300</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44425</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44306</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44440</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44225</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>44466</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44140</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44711</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44132</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44706</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44342</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44596</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44131</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44207</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44608</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44657</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44579</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45035</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45106</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45761</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44284</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>44517</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44302</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45027</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44132</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44698</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45079</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45573</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44235</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45217</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45713</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>44967</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45212</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44700</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45631</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45744</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45183</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44120</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44998</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45579</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45108</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45643</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44747</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45107</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45340</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44860</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44911</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44890</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44616</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44875</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45538</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45012</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45092</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44909</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45019</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45635</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44433</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45118</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44302</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>44936</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45166</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44753</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45362</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45034</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>44862</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45685</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45587</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44553</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45117</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45266</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45142</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>44847</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44930</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45693</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44305</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45057</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>44693</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44323</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>44967</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45020</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45113</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45162</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>44879</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45077</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45301</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44281</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45030</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44942</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>44323</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44981</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45554</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>44596</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45048</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45719</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45015</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45075</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45625</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45610</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45538</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45594</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45344.695</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45499</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45328</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44706</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>45621</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45551</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44398</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45782</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45483</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45335</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>44757</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>45324</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45127</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45785</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45512</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44543</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45707</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45328</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45107</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45103</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44350</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45754</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45749</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>44496</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>44930</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45453</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45475</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45234</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45755</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45082</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>44636</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45085</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45568</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44988</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44584</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>44592</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45358</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44614</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44559</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45551</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45303</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45085</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>44799</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44302</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45538</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>44349</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45443</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>44169</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45766</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45057</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45475</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>44754</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45092</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45483</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>45770</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44903</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45069</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45238</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44837</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45841</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44580</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45012</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45334</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45600</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45245.655</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45050</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45204</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>44284</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45827</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45532</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>44881</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45581.49081018518</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45254</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>44920</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45733</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>45733</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45697</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45048</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>45733</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45733</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44825</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45085</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45085</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45055</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>44586</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45683</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>44820</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>44200</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>44725</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44988</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45722</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>44441</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>44516</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45080</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>45783</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>44186</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45247</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>44435</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45174</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45443</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45499</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44523</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45524</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>44866</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>44305</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>44204</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45264</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45126</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45558</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45093</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>44080</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>44235</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45561</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>45238</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>45662</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45631</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>44636</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45342</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44309</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45707</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>44624</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>44939</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45832</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>45178</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>44860</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>44893</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44820</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45142</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45050</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45251</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>45316</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44139</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45094</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45714</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45084</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44461</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>45335</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45839</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45838</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45880</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45846</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45880</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45711</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45140</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45256</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>44619</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45180</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45772</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45133</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45846</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45181</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45631</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45887.44987268518</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45133</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45887.44877314815</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>44874</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>45887.44629629629</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45887.49454861111</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45846</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45324</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45170</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45042</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45162</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>44144</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>44893.475</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45602</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45415</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45733.43296296296</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45891.58806712963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45091</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45890</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45085</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45012</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45159</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44461</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48998,7 +48998,7 @@
         <v>45092</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45657</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>44742</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49568,7 +49568,7 @@
         <v>44628</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45148</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45037</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44531</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44140</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>44467</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44445</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45050</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>44237</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44139</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44139</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45809</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44159</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45337</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44208</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44083</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44113</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44124</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44179</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44356</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44273</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44279</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44140</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44572</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44551</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44074</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44342</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44152</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44285</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44284</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44585</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44600</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44120</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44585</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>44468</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44687</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44670</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44458</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44325</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44139</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44501</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44421</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44406</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44449</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44368</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44441</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44384</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44375</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44705</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44435</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44222</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44103</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44167</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44365</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44399</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44241</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44498</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44462</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44140</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44497</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44806</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44343</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44154</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44132</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44424</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44256</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44624</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44442</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44874</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44742</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44259</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44208</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44629</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44364</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44267</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44350</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44441</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44501.61</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44572</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44420</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44599</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44300</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44491</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44270</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44267</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44088</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44476</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44123</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44088</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44623</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44188</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44333</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44440</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44365</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44322</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>44209</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>44305</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44075</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44113</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44687</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44204</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44208</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44217</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44425</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44440</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44146</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44466</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44847</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44286</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44300</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44306</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44225</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44259</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44140</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>44706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44132</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44711</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44131</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44596</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44342</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44207</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44608</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>44579</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44284</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44302</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>44133</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44132</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>44698</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>44657</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>44858</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45042</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45683</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44621</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45362</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44881</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45733</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45733</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45245.655</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45713</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45204</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45247</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44309</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45512</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44825</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45092</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45600</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45766</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45342</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45538</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45621</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45551</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45075</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45625</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45344.695</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45499</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45594</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>44860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45782</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45107</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>44398</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44628</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44903</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45107</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44967</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45126</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45133</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44879</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44866</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45020</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45785</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44461</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45475</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45453</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45315</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45127</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45443</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>44981</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45084</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45415</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>44512</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44496</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45048</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45181</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45483</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44559</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45335</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>44473</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45358</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44939</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45475</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45030</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44837</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45770</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44596</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>44144</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45841</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45719</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45499</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44893.475</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45524</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44305</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44592</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45012</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45631</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45551</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44584</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45334</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45558</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44988</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45050</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44614</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44523</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45328</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45554</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>44624</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>45162</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>44169</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44799</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44636</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45092</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>44586</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45170</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45742</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45643</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>44754</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45714</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45783</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>44911</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>44200</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45057</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>44725</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>44204</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>44706</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45707</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45657</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45693</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>44693</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45761</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>44920</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45324</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45133</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44186</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44616</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45561</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45057</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45142</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45832</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45697</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45085</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44742</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45722</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45012</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45015</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>44619</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>44967</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45316</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>44700</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45092</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45256</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45079</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45880</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45839</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45880</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45238</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45266</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45838</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45880</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>45180</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>44820</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45711</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45117</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44936</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45055</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45004</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45887.44877314815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>44862</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45887.44987268518</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45887.44629629629</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45887.49454861111</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45142</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45890</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>44753</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45178</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45303</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45685</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45019</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>44354</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>44874</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>45166</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>44323</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>44636</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45140</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45894.39850694445</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45891.58806712963</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45070</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>44281</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45896.55240740741</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44747</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45301</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45846</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>44349</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45846</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45335</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44820</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45827</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44350</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45898.32637731481</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>44080</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45897.45144675926</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45754</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45602</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45089</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45148</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44893</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>44517</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>44988</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45610</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>44516</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45027</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45113</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>44543</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44930</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44748</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44435</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44235</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45183</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45238</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45744</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44890</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45080</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>44235</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44323</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>45077</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>44090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>44284</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45166</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45579</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44120</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45162</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45532</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44741</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45264</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45635</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44302</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44580</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>44461</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>44860</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45234</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>44139</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45538</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45538</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>44909</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43516,7 +43516,7 @@
         <v>45091</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45035</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45092</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>44847</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45568</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45568</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45772</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45069</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44441</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>44930</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>44942</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45103</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45108</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45733</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45733</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45050</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>44875</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45573</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45106</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>44998</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45324</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45012</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>45085</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45340</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>45159</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45048</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45085</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>44305</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45254</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45174</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45662</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45251</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45094</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45212</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45707</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45443</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45328</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45034</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48998,7 +48998,7 @@
         <v>45085</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>45085</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45082</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45483</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45118</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45749</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49568,7 +49568,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45631</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45587</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45037</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44531</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44140</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>44467</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44445</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45050</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>44237</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44139</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44139</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45809</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44159</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45337</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44208</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44083</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44113</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44124</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44179</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44356</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44273</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44279</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44140</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44572</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44551</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44074</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44342</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44152</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44285</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44284</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44585</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44600</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44120</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44585</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>44468</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44687</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44670</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44458</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44325</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44139</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44501</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44421</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44406</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44449</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44368</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44441</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44384</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44375</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44705</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44435</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44222</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44103</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44167</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44365</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44399</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44241</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44498</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44462</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44140</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44497</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44806</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44343</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44154</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44132</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44424</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44256</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44624</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44442</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44874</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44742</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44259</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44208</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44629</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44364</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44267</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44350</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44441</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44501.61</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44572</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44420</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44599</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44300</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44491</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44270</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44267</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44088</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44476</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44123</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44088</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44623</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44188</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44333</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44440</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44365</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44322</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>44209</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>44305</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44075</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44113</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44687</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44204</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44208</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44217</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44425</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44440</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44146</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44466</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44847</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44286</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44300</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44306</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44225</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44259</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44140</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>44706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44132</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44711</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44131</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44596</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44342</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44207</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44608</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>44579</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44284</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44302</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>44133</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44132</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>44698</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>44657</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>44858</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45042</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45683</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44621</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45362</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44881</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45733</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45733</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45245.655</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45713</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45204</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45247</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44309</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45512</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44825</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45092</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45600</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45766</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45342</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45538</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45621</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45551</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45075</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45625</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45344.695</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45499</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45594</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>44860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45782</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45107</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>44398</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44628</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44903</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45107</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44967</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45126</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45133</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44879</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44866</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45020</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45785</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44461</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45475</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45453</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45315</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45127</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45443</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>44981</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45084</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45415</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>44512</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44496</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45048</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45181</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45483</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44559</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45335</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>44473</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45358</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44939</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45475</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45030</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44837</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45770</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44596</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>44144</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45841</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45719</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45499</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44893.475</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45524</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44305</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44592</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45012</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45631</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45551</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44584</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45334</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45558</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44988</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45050</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44614</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44523</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45328</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45554</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>44624</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>45162</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>44169</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44799</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44636</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45092</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>44586</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45170</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45742</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45643</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>44754</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45714</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45783</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>44911</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>44200</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45057</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>44725</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>44204</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>44706</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45707</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45657</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45693</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>44693</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45761</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>44920</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45324</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45133</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44186</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44616</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45561</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45057</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45142</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45832</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45697</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45085</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44742</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45722</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45012</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45015</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>44619</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>44967</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45316</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>44700</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45092</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45256</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45079</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45880</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45839</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45880</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45238</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45266</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45838</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45880</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>45180</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>44820</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45711</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45117</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44936</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45055</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45004</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45887.44877314815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>44862</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45887.44987268518</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45887.44629629629</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45887.49454861111</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45142</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45890</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>44753</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45178</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45303</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45685</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45019</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>44354</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>44874</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>45166</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>44323</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>44636</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45140</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45894.39850694445</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45891.58806712963</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45070</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>44281</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45896.55240740741</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44747</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45301</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45846</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>44349</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45846</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45335</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44820</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45827</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44350</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45898.32637731481</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>44080</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45897.45144675926</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45754</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45602</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45089</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45148</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44893</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>44517</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>44988</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45610</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>44516</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45027</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45113</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>44543</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44930</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44748</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44435</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44235</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45183</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45238</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45744</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44890</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45080</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>44235</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44323</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>45077</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>44090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>44284</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45166</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45579</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44120</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45162</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45532</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44741</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45264</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45635</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44302</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44580</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>44461</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>44860</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45234</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>44139</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45538</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45538</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>44909</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43516,7 +43516,7 @@
         <v>45091</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45035</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45092</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>44847</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45568</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45568</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45772</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45069</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44441</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>44930</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>44942</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45103</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45108</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45733</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45733</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45050</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>44875</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45573</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45106</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>44998</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45324</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45012</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>45085</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45340</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>45159</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45048</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45085</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>44305</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45254</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45174</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45662</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45251</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45094</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45212</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45707</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45443</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45328</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45034</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48998,7 +48998,7 @@
         <v>45085</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>45085</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45082</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45483</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45118</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45749</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49568,7 +49568,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45631</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45587</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44509</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>45905.57458333333</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45037</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44132</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>44531</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44140</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>44467</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>44237</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44139</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45050</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>45809</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44139</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44445</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44159</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45337</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44208</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>44083</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>44113</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44124</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44166</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44179</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44279</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44356</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>44273</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>44140</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>44572</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44551</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>44342</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>44285</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44152</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44284</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44585</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44120</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44468</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>44585</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>44687</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>44670</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44458</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>44325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44139</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44501</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44421</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44368</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44406</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44449</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>44441</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>44384</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>44375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44705</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44435</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44103</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44222</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44167</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>44365</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44399</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44241</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>44503</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>44498</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>44140</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44497</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>44806</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>44343</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44154</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44132</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44256</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>44424</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44874</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44442</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>44624</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>44259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44208</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44629</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44267</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44364</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>44350</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>44441</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44501.61</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>44572</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44420</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44599</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44491</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>44300</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>44267</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44270</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44452</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44476</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44123</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44088</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44623</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44188</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>44440</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44742</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44322</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44305</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44747</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>44113</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>44687</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44208</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44125</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44204</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44425</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44847</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>44440</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>44466</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44259</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>44146</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44286</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44217</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44140</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44300</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>44306</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44711</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44706</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44225</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44132</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44342</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44608</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44579</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44131</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44596</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44207</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44133</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44657</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44858</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44365</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44284</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>44302</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44132</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>44698</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45019</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45035</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>45635</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>44209</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44621</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>44333</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45166</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45362</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45301</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44281</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45030</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44748</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45048</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45075</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45625</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45538</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45594</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45344.695</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45499</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45034</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45685</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>45621</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>44398</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45077</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45782</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44942</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44553</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45142</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45785</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>44847</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>44323</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45079</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44305</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>44981</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44967</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44323</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45004</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44967</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>44596</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>44998</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>45108</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45020</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>45610</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45551</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44496</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45453</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45643</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45475</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>44747</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45107</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>44860</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>44890</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45127</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>44875</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45315</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45162</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>44879</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>45512</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>44741</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>44543</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45791.4247337963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45554</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45719</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45015</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45754</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45358</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44930</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44706</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44559</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45082</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45085</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45483</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45335</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>44757</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45324</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45707</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45328</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45107</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>44614</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45103</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44350</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45770</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45551</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45749</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45085</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>44799</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>44302</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45234</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>45538</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>44837</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45841</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44349</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44636</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44169</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45568</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45568</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44988</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45766</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>45057</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45012</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44584</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>44754</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>44592</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>45092</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45483</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>44903</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45303</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45238</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44512</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44580</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45443</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45475</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45050</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29062,7 +29062,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44284</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45742</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>44881</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>44920</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45783</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>45055</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45069</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>44988</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45722</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>44441</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45080</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45600</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45245.655</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45561</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>45204</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45247</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>45832</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45532</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45839</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45838</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45880</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45880</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45711</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45880</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45256</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45846</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44435</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45887.44987268518</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45254</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45887.44877314815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45887.44629629629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45887.49454861111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45733</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45733</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45499</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>45891.58806712963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45890</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45697</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45827</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45048</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45733</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45733</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44825</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45524</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44354</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45085</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>45085</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45894.39850694445</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45846</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45896.55240740741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45897.45144675926</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44586</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45898.32637731481</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>45683</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>44305</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45903</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45903.83215277778</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>44204</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45264</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45905</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>44820</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>45905.428125</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>44200</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45093</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>44080</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>44725</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45905.46513888889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>44235</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>44516</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>44914.59483796296</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>45905</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44186</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45238</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45662</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45631</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44624</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44939</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45174</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45443</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44523</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45178</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>44893</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38844,7 +38844,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>44820</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45126</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45142</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>45558</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44139</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>45094</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>44636</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45342</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>44309</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45707</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>44860</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>45140</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>45105.41813657407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45050</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45104</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>45251</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45316</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>44619</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>45180</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45714</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45084</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>44461</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45335</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45181</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42321,7 +42321,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45324</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45042</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45162</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>44893.475</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>45772</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45133</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45602</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>45092</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45631</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45133</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44874</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45085</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>44144</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45166</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>44461</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>45415</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45091</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>45092</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45657</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45012</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45159</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45761</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>44517</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45027</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45573</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>44235</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>44742</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>44700</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>45744</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45183</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>44628</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45089</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>44120</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>44616</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>45070</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46710,7 +46710,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>45037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45092</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>44909</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45217</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>45713</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>45212</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>45631</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>45579</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45266</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>45340</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47793,7 +47793,7 @@
         <v>44090</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>44911</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45538</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45012</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48477,7 +48477,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48591,7 +48591,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>44433</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45118</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>45057</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>44693</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49104,7 +49104,7 @@
         <v>44302</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>44936</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44753</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45113</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>44862</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49731,7 +49731,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49788,7 +49788,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45587</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49959,7 +49959,7 @@
         <v>45117</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>44930</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50358,7 +50358,7 @@
         <v>45693</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>44473</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>45911</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>44509</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44960</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45901</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45905</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44132</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44531</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>44140</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44445</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44467</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45050</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44237</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>44139</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>44139</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45809</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>44159</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45337</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44208</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44113</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44124</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>44179</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44166</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44279</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44356</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44273</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44572</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44140</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44551</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44342</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44152</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44284</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>44285</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44585</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44120</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44468</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44585</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44687</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44670</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44458</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44139</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>44501</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44421</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44368</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44406</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44449</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44441</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>44384</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44435</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44705</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44103</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44222</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44167</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44365</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44399</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44498</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44503</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>44140</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>44241</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44497</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44806</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44343</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44154</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44132</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44424</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44624</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44442</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44874</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44208</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>44629</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44364</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44267</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44350</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>44441</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44501.61</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44572</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44420</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44599</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44300</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44491</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44270</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44452</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44476</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44123</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44088</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44623</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44188</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44209</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>44440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44742</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44322</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44365</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44113</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44305</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44125</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44146</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44286</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44208</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44687</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>44140</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44425</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44440</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44847</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44466</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44711</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44259</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44706</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44131</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44342</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44204</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44608</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44579</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44657</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44858</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44133</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44309</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45512</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>44284</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>44825</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44302</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44132</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44698</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45042</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44217</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45683</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>45362</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44881</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>45204</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44300</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44621</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45092</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45713</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45247</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45733</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45733</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44306</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45245.655</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45600</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>44225</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45766</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44860</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45342</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45538</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45551</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44903</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45621</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45075</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45625</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45344.695</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45499</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45594</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44967</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45107</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44132</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45782</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44628</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45107</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44398</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>45133</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45126</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44879</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45020</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44866</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44461</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>44981</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45475</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45084</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45453</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45315</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45415</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44512</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45127</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45048</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45443</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>44596</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44207</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44496</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45181</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44559</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44473</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44596</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45719</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45358</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44305</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44939</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45475</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45631</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45030</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45558</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>44144</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44837</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45770</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44553</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44523</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45328</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45499</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>44893.475</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45841</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>44624</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45524</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45162</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>44169</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45012</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>44592</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44799</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45551</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45092</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44586</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45334</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44584</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45170</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44988</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45643</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45050</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44754</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44614</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45714</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45554</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>45057</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45742</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44725</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44706</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45707</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45693</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45761</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44911</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>44200</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45133</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45783</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>44616</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45697</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>44204</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44742</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45657</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>44693</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>44920</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44757</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45324</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>44186</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>45561</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>45832</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45057</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45142</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>45238</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45180</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>44820</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45085</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>45722</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45012</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45015</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>44619</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44967</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45316</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44700</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45256</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45092</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45079</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44862</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>45266</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45117</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44936</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45055</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45880</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45839</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45880</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>45004</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>44753</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45838</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45142</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45631</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45303</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45178</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>45685</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>44323</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45880</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45019</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45166</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44747</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>44349</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>44636</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45711</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>44820</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>45140</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45070</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>44281</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>45301</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45148</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>44988</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>44516</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45335</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45027</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45113</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44930</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44748</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44435</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45238</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45744</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>44890</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44350</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45080</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45077</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>44090</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45166</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>45532</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45602</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45089</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45264</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44302</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44461</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44860</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45234</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45538</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44893</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45538</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44517</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45091</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45610</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45887.44877314815</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45092</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44543</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44847</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45887.44987268518</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45772</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45887.44629629629</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45887.49454861111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>44930</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>44235</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45890</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45183</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45103</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45108</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45733</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45733</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45050</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>44235</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>44354</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44323</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45894.39850694445</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43131,7 +43131,7 @@
         <v>45891.58806712963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>44284</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>45896.55240740741</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>45579</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>45846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>44120</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45827</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45162</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>44741</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45898.32637731481</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45635</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45217</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>44580</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45897.45144675926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44139</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>44909</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45035</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44561,7 +44561,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45903</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45568</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45568</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45903.83215277778</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45905</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>45069</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44441</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45905</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45905.46513888889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>45908.49148148148</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45905</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45104</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45908.58891203703</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>44942</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>45910.43229166666</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>44875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45910</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45573</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>45106</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>45911.66232638889</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46737,7 +46737,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44998</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>45324</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>45012</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47027,7 +47027,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45085</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47141,7 +47141,7 @@
         <v>45340</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45159</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47654,7 +47654,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>45085</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44305</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>45254</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>45174</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45662</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45251</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45094</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45212</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45707</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45443</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>45328</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45034</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49250,7 +49250,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>45085</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49421,7 +49421,7 @@
         <v>45085</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45483</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45118</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45749</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45631</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45587</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>45911</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>44509</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44960</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45901</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45905</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44132</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44531</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>44140</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44445</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44467</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45050</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44237</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>44139</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>44139</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45809</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>44159</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45337</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44208</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44113</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44124</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>44179</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44166</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44279</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44356</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44273</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44572</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44140</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44551</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44342</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44342</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44152</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44284</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>44285</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44585</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44120</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44468</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44585</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44687</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44670</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44458</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44139</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>44501</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44421</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44368</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44406</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44449</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44441</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>44384</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44435</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44705</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44103</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44222</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44088.34521990741</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44167</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44365</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44399</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44498</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44503</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>44140</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>44241</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44497</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44806</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44343</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44154</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44132</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44424</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44624</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44442</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44874</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44208</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>44629</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44364</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44267</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44350</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>44441</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44501.61</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44572</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44420</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44599</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44300</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44491</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44270</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44452</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44476</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44123</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44088</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44623</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44188</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44209</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>44440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44742</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44322</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44365</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44113</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44305</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44125</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44146</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44286</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44208</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44687</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>44140</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44425</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44440</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44847</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44466</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44711</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44259</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44706</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44131</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44342</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44204</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44608</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44579</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44657</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44858</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44133</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44309</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45715.39251157407</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45512</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>44284</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>44825</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45334.4565162037</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44302</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45343.56496527778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44132</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44698</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45042</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44217</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45683</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44825.97048611111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45208.83212962963</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>45362</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44881</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45180.62233796297</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45407.61273148148</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>45334.63445601852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>45204</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44300</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44621</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>45321.65413194444</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45092</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45713</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45247</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45715.38833333334</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45733</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45733</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44306</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45194.60591435185</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45245.655</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45495.63521990741</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45600</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>44225</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45766</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45344.35084490741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44551.40351851852</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44860</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45545.58982638889</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45106.43407407407</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45342</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44445.65237268519</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45225.8025</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45538</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45551</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44903</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45393.66436342592</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45621</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45075</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45625</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45344.695</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45499</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45594</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44967</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45107</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44132</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45782</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44628</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>45093.50841435185</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45161.47722222222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45107</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44398</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45002.57140046296</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>45133</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45577.29355324074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45126</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44879</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45020</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44866</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45526.70548611111</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45156.6415162037</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45394.58707175926</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45531.94460648148</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44461</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45035.43935185186</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45035.44078703703</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>44981</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45524.35208333333</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45475</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45084</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45106.36304398148</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45573.72731481482</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45453</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45315</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45127.48940972222</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45415</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44512</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45127</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45048</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45443</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45076.50148148148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45174.49248842592</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>44596</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44207</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44496</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45181</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44581.97131944444</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45309.69809027778</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45334.6330787037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44559</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44473</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44596</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45719</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45358</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44305</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44939</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44939.68549768518</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45475</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45218.49332175926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45631</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45673.28958333333</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45512.47371527777</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45030</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45558</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>44144</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44837</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45770</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44553</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44523</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45328</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45499</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>44893.475</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45841</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>44624</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45524</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45747.50460648148</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45162</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>44169</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45012</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>44592</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44799</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45647.38805555556</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45162.56537037037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45551</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45092</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44586</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45334</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44584</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45170</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45194.39523148148</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>45095.39417824074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44988</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45643</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45050</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44754</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44614</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45714</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45062.38267361111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45645.35019675926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45645.3549537037</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45090.87483796296</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45554</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>45057</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45616.35783564814</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45742</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44725</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44706</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45707</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45693</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45761</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45210.40899305556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45699.59120370371</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45565.79476851852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44911</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>44200</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45133</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45783</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45173.44273148148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>44616</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45637.38047453704</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45697</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>44204</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44742</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45657</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>44693</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44711.57103009259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45169.45913194444</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45821.57865740741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45826.44898148148</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>44920</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44757</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45826.49226851852</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45324</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44973.29771990741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45826.44643518519</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>44186</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45827.41407407408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>45629.63384259259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>45827.41166666667</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>45251.80934027778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45827.41239583334</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45827.45193287037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>45561</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45827.45453703704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45832.43682870371</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>45832</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45057</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45142</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>45832.58216435185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>45238</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45812.6565625</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45180</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>44820</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45085</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45576.86913194445</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45875.60789351852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45875.66709490741</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45832.87938657407</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>44638.56855324074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>44722.55038194444</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>45722</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45012</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45015</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45876.42027777778</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>44619</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45309.69599537037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44967</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45350.39834490741</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45309.69259259259</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45316</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44700</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45875.60252314815</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>45835.58707175926</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45873.57835648148</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45256</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45630.58119212963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45092</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45875.61711805555</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45308.40855324074</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45079</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45361.81741898148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44862</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>45266</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44757.34600694444</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45117</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44936</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45055</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45880</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45839</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45880</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>45004</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45062.38054398148</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>44753</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45309.44398148148</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45278.72490740741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45358.64158564815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45839.70422453704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45839.706875</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45838</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45142</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45631</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45303</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45178</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45728.69217592593</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>44295.58509259259</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>45685</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45749.69665509259</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>44323</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45880</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45019</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45736.44543981482</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45166</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44747</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>44474.8949537037</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>44349</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>44636</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>44585.33765046296</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45711</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>44820</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>45140</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45070</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>44281</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45645.87954861111</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>45301</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45148</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>44988</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>45344.29208333333</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>44840.58092592593</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>44516</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45883.50228009259</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45335</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45027</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45703.81983796296</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45113</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45204.62678240741</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45747.84215277778</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44930</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44748</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44435</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45238</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45744</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>44890</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44530.55888888889</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44350</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45883.50537037037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45884.3334837963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45080</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45075.43681712963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45077</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>44090</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45166</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>44636.83194444444</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>45532</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45602</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45089.43696759259</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45089</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45735.7075462963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45264</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44302</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44461</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44860</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45234</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45538</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44893</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45538</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44517</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45091</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45393.30375</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45610</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45695.37408564815</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45887.44877314815</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45351.67325231482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45406.73519675926</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45013.44094907407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45092</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44543</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44847</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44603.56049768518</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45092.68969907407</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45887.44987268518</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45772</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>44285.43282407407</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45887.44629629629</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45812.65798611111</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45887.49454861111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>44930</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45624.45537037037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>44235</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45890</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45847.5694212963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45847.65952546296</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45183</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45103</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45108</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45733</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45733</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45050</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>44235</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>44354</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44323</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45894.39850694445</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43131,7 +43131,7 @@
         <v>45891.58806712963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>44284</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>45896.55240740741</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>45579</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>45846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>44120</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45827</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45169.6147337963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45162</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>44741</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45898.32637731481</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45635</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45217</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>44580</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45897.45144675926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44139</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45166.49883101852</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>44909</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45035</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45013.43306712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45013.43763888889</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44561,7 +44561,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>44930.78150462963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45903</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45568</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45568</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45245.50461805556</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45903.83215277778</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45531.4630787037</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45905</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>45069</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44441</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45905</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45905.46513888889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>45908.49148148148</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45735.96366898148</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45602.58842592593</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45602.61121527778</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45905</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>45789.45869212963</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45580.72222222222</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45104</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45908.58891203703</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>44942</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>45910.43229166666</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45154.94172453704</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>44875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45910</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45573</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>45106</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>45911.66232638889</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44900.59222222222</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46737,7 +46737,7 @@
         <v>45195.77855324074</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44998</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>45324</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>45012</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47027,7 +47027,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45085</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47141,7 +47141,7 @@
         <v>45340</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45159</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>44903.44068287037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>45370.63612268519</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45674.37722222223</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>45135.61125</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45454.72009259259</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>44991.60873842592</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47654,7 +47654,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>45085</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44305</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>45551.91032407407</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45168.89541666667</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>45254</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>45174</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45662</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>45251.80711805556</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45251</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>45182.43038194445</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45223.50019675926</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45094</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45212</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45619.67202546296</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45707</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45443</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>45328</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45034</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45393.86842592592</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>45154.93615740741</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49250,7 +49250,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>45106.36086805556</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>45085</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49421,7 +49421,7 @@
         <v>45085</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45483</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>45092.64113425926</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45118</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>45571.82802083333</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45749</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45727.53451388889</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45631</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45587</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45250.37905092593</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45698.47751157408</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>45737.66008101852</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -567,7 +567,7 @@
         <v>45832</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>45911</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>44509</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44960</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45918</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>45905</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45603.46306712963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45826.50638888889</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45037</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45901</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45924.48732638889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>44132</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44531</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>44467</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45002.64284722223</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44140</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44139</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45050</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44139</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>44445</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45826.49623842593</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44159</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>45579.41793981481</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45110.59303240741</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45337</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45809</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44208</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>44279.88631944444</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>44245.49747685185</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>44113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>44124</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44242.35074074074</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>44166</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44249.57096064815</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>44179</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44273</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44279</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>44574.53206018519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>44140</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44368.68505787037</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44572</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44551</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>44869.37805555556</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44432.52225694444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44342</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44342</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44152</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44284</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>44285</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44585</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>44600</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>44120</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>44585</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>44687</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>44468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44273.4187962963</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44830.46083333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44875.43988425926</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44875.4530787037</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44458</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44483.831875</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44325</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44139</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>44501</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>44350.5575925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44559.5102662037</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44421</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>44152.70959490741</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>44691.62895833333</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44406.65106481482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44368</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>44449</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44526.64325231482</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44411.27403935185</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44441</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44462.38528935185</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44659.49101851852</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>44314.85686342593</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44384</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44676.45043981481</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44629.93263888889</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>44502</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44285.43686342592</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44361.36178240741</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44375</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>44435</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44705</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44222</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44103</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44167</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44365</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44399</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44241</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44719.61128472222</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44447.68054398148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44503</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44462</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>44498</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44140</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44497.92861111111</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>44497</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44806</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44361.59884259259</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>44343</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>44206.42408564815</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>44154</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44132</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44424</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44442</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>44624</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44874</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>44742</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>44208</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44629</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44364</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44267</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>44441.76258101852</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>44305.43628472222</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44374.73391203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>44441</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44501.61</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44434.60960648148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44572</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44571.43729166667</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44446.44287037037</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44420</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>44117.39789351852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44300</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44270</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44266.84585648148</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44433.9015162037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44491</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>44314.85135416667</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>44452</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>44588.36425925926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44476</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44123</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>44377.74945601852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>44516.53758101852</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44623</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44188</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44270.41763888889</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44859.4846412037</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>44365</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44460.67511574074</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44484.50790509259</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44333</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>44440</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44302.44891203703</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>44742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>44322</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>44295.56783564815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>44305</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44743.61866898148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44747</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44719.63167824074</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>44295.57456018519</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44113</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>44494.57087962963</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44687</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44467.70932870371</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>44467.71108796296</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44204</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44627.9332175926</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44627.93427083334</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44634.57651620371</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44825.96707175926</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44208</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44209</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44125</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>44285.50226851852</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44480.49596064815</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>44217</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>44425</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>44440</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44592.6608912037</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44466</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44847</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44466.88909722222</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>44259</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44837.44972222222</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>44300</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44320.52675925926</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44306</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44225</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>44706</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>44131</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44540.59521990741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44132</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44475.35071759259</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44524.55496527778</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44809.58320601852</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>44596</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44207</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44284</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44302</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44286.89717592593</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44439.56229166667</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>44399.59900462963</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44356.48402777778</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44132</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44698</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44608</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44579</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44543.56502314815</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44136.79652777778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44133</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44621</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45615.4612037037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45004</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45180.4958449074</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45387.38211805555</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45672.66238425926</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45301</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44281</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45030</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45348.55489583333</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44998</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45393.36715277778</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45108</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44748</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45775.59717592593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45531.50513888889</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45643</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45048</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45107</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45537.91339120371</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44860</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45028.56200231481</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>44890</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45075</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44875</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45604.45568287037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45625</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45495.64009259259</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45075.44275462963</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45538</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44608.61462962963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45594</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>44741</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>44946.48041666667</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45555.36652777778</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45344.695</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44939.68818287037</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45012.60288194445</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45373.49626157407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45499</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44809.41969907407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45372.46738425926</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44672.62571759259</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45573.91842592593</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45621</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45051.33702546296</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44398</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44756.55196759259</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45458.75857638889</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45077</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45635</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45782</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>44942</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45783.29873842592</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45215.35577546297</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45756.60606481481</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45604.4915625</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44937.66680555556</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45107.6715625</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>44728.67653935185</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45695.37572916667</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45783.38400462963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45783.43942129629</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45387.90001157407</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45166</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45469.37361111111</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45362</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45034</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>45685</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>44323</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44981</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45159.43704861111</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45784.28789351852</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45784.29160879629</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45610.38868055555</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>44596</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45624.8330324074</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45784.5990625</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45784.60247685185</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45784.28640046297</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45674.37980324074</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>44986.33892361111</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>44553</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         <v>45714.8555324074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45610</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44692.459375</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45578.38111111111</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45142</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44876.36309027778</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45631.39092592592</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44146</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45551</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45747.85570601852</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45785.77976851852</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44286</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45127</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45512</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45166.6434375</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>44543</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45789.66337962963</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45785.77806712963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45198.56633101852</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>44496</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44503.58373842593</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44847</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45002.62616898148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45028.55498842592</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44545.34950231481</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44305</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45656.2784375</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45453</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45754.36746527778</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44847.67832175926</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45261.4658449074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45475</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45691.70079861111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45532.43490740741</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45384.68908564815</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45540.63275462963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44140</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45001.50576388889</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44967</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45366.65268518519</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45075.43525462963</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45266.39518518518</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44711</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45020</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44592.63900462963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45202.53679398148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45075.52633101852</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44930</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45162</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>44879</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45790.36726851852</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45013.82003472222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>44272.41576388889</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45720.43899305556</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45082</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45028.55811342593</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45358</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45712.92822916667</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45014.91954861111</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45085</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>44342</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>44804.88839120371</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>44614.48950231481</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45554</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44559</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45796.37314814814</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45586.77130787037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>45719</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45015</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45107.66918981481</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44614</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45007.47481481481</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45007.48090277778</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>45215.46303240741</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45797.42636574074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45797.42967592592</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45551</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44691.62384259259</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45085</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44799</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44641.60950231482</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44302</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45796.47753472222</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45077.43820601852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44691.63315972222</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45537.91421296296</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45538</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45328</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45393.30091435185</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45170.64689814814</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>44706</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>44657</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>44858</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>44875.45777777778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45797.43391203704</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>44169</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45166.65524305555</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45251.55815972222</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>44631.65131944444</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45743.55949074074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45715.38768518518</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45463.42392361111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45463.42876157408</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45766</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45057</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45693.46003472222</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45727.46905092592</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45581.36192129629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45335</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44757</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44754</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45324</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45092</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44930.83994212963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44851.64682870371</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44593.45266203704</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45770</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45707</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45328</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45107</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45799.63540509259</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45009.46116898148</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45103</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45455.45792824074</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44903</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45632.59701388889</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45841</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>44200.41072916667</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45012</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45400.9021412037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45238</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45334</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45393.93069444445</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>44511.57038194445</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45775.63248842592</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>44350</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45733.42858796296</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44580</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>45035</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45456.68532407407</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45315.87924768519</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45234</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45541.33905092593</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45043.65984953703</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45050</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45568</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45568</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45028.54530092593</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45028.55927083334</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44988</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>44584</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45168.8937962963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>44592</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>44284</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45266.39803240741</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45772.43194444444</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>45809.60372685185</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>45365.30353009259</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45303</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45113.47337962963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>44881</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45537.49834490741</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>44920</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45085.57921296296</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>45756.60348379629</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45756.60971064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45443</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45817.63003472222</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45475</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45001.70106481481</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>45055</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45278.56393518519</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44587.5346412037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45537.50579861111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45553.63233796296</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44545.89236111111</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45610.89532407407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45742</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44886.58100694444</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45674.37481481482</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45315.89215277778</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44988</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45079</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>45664.61196759259</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44960.28089120371</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45257.79081018519</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45722</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44441</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>45196.41784722222</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44491.33081018519</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44967</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45279.34813657407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45069</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>45387.88914351852</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>45532.43672453704</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45532.43798611111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45387.37787037037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45080</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45238.3500462963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45247</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>45243.34587962963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>44435</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45105.41936342593</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45218.40603009259</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>45106.3509837963</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45681.87600694445</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44974.82748842592</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>45600</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45245.655</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45499</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45165.53146990741</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45204</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45532</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45524</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45747.87305555555</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45218.4927662037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45254</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>45537.4990625</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45218.41484953704</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>44866</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45733</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45733</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45013.65112268519</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>44305</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>45411.41958333334</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44204</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45048</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45733</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45733</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>44609.5427199074</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>44609.55334490741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>44825</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45264</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45085</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45085</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45188.45027777777</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44586</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45093</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45664.61273148148</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>44820</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>44235</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45113.47484953704</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44200</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44725</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>45225.77278935185</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44914.59365740741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557